--- a/documentacion/Plan_Tesis_2026_Gantt_Seguimiento.xlsx
+++ b/documentacion/Plan_Tesis_2026_Gantt_Seguimiento.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\UPMH - Maestría en Inteligencia Artificial\Sexto cuatrimestre\Tesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\tesis\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF14E0C-D21C-4B61-9CFB-BCDD7B596B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388ADF95-472C-455E-92A6-F9B8641C554E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma Tesis (V2)" sheetId="2" r:id="rId1"/>
@@ -895,20 +895,20 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.42578125" customWidth="1"/>
-    <col min="4" max="5" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.44140625" customWidth="1"/>
+    <col min="4" max="5" width="11.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="4" customWidth="1"/>
     <col min="7" max="7" width="11" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="4.88671875" customWidth="1"/>
     <col min="18" max="30" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1028,7 +1028,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M5" s="6"/>
     </row>
-    <row r="6" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -1191,7 +1191,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="R11" s="6"/>
     </row>
-    <row r="12" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -1292,14 +1292,14 @@
         <v>1</v>
       </c>
       <c r="G12" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H12" t="s">
         <v>85</v>
       </c>
-      <c r="S12" s="11"/>
-    </row>
-    <row r="13" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S12" s="6"/>
+    </row>
+    <row r="13" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>11</v>
       </c>
@@ -1319,15 +1319,15 @@
         <v>3</v>
       </c>
       <c r="G13" s="10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" t="s">
         <v>50</v>
       </c>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-    </row>
-    <row r="14" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+    </row>
+    <row r="14" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>12</v>
       </c>
@@ -1347,14 +1347,14 @@
         <v>1</v>
       </c>
       <c r="G14" s="10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
         <v>50</v>
       </c>
-      <c r="V14" s="5"/>
-    </row>
-    <row r="15" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V14" s="11"/>
+    </row>
+    <row r="15" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>13</v>
       </c>
@@ -1382,7 +1382,7 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>14</v>
       </c>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Y16" s="5"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>15</v>
       </c>
@@ -1437,7 +1437,7 @@
       <c r="Z17" s="5"/>
       <c r="AA17" s="5"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>16</v>
       </c>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AB18" s="5"/>
     </row>
-    <row r="19" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>17</v>
       </c>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AC19" s="5"/>
     </row>
-    <row r="20" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>18</v>
       </c>
@@ -1532,20 +1532,20 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AV23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="4" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="4.88671875" customWidth="1"/>
     <col min="18" max="48" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1719,7 +1719,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1775,7 +1775,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1804,7 +1804,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1832,7 +1832,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1860,7 +1860,7 @@
       <c r="T7" s="6"/>
       <c r="U7" s="6"/>
     </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1888,7 +1888,7 @@
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
     </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1916,7 +1916,7 @@
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
     </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1944,7 +1944,7 @@
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
     </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="AB11" s="5"/>
     </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2000,7 +2000,7 @@
       <c r="AD12" s="5"/>
       <c r="AE12" s="5"/>
     </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2028,7 +2028,7 @@
       <c r="AF13" s="5"/>
       <c r="AG13" s="5"/>
     </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AH14" s="5"/>
     </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2083,7 +2083,7 @@
       <c r="AI15" s="5"/>
       <c r="AJ15" s="5"/>
     </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2111,7 +2111,7 @@
       <c r="AK16" s="5"/>
       <c r="AL16" s="5"/>
     </row>
-    <row r="17" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
     </row>
-    <row r="18" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2167,7 +2167,7 @@
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
     </row>
-    <row r="19" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AQ19" s="5"/>
     </row>
-    <row r="20" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="AR20" s="5"/>
       <c r="AS20" s="5"/>
     </row>
-    <row r="21" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="AT21" s="5"/>
       <c r="AU21" s="5"/>
     </row>
-    <row r="22" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="AV22" s="5"/>
     </row>
-    <row r="23" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>

--- a/documentacion/Plan_Tesis_2026_Gantt_Seguimiento.xlsx
+++ b/documentacion/Plan_Tesis_2026_Gantt_Seguimiento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\tesis\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388ADF95-472C-455E-92A6-F9B8641C554E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48502D85-39C7-4945-B39D-D52C1BD3DF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma Tesis (V2)" sheetId="2" r:id="rId1"/>
@@ -1352,7 +1352,7 @@
       <c r="H14" t="s">
         <v>50</v>
       </c>
-      <c r="V14" s="11"/>
+      <c r="V14" s="6"/>
     </row>
     <row r="15" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
@@ -1379,7 +1379,7 @@
       <c r="H15" t="s">
         <v>50</v>
       </c>
-      <c r="W15" s="5"/>
+      <c r="W15" s="11"/>
       <c r="X15" s="5"/>
     </row>
     <row r="16" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">

--- a/documentacion/Plan_Tesis_2026_Gantt_Seguimiento.xlsx
+++ b/documentacion/Plan_Tesis_2026_Gantt_Seguimiento.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\tesis\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48502D85-39C7-4945-B39D-D52C1BD3DF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F47E95C-8714-41C0-B8AC-26A50C4F7FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma Tesis (V2)" sheetId="2" r:id="rId1"/>
-    <sheet name="Cronograma Tesis" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
   <si>
     <t>ID</t>
   </si>
@@ -113,60 +112,6 @@
     <t>S22</t>
   </si>
   <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>S33</t>
-  </si>
-  <si>
-    <t>S34</t>
-  </si>
-  <si>
-    <t>S35</t>
-  </si>
-  <si>
-    <t>S36</t>
-  </si>
-  <si>
-    <t>S37</t>
-  </si>
-  <si>
-    <t>S38</t>
-  </si>
-  <si>
-    <t>S39</t>
-  </si>
-  <si>
-    <t>S40</t>
-  </si>
-  <si>
     <t>Planeación</t>
   </si>
   <si>
@@ -209,57 +154,18 @@
     <t>Análisis</t>
   </si>
   <si>
-    <t>Análisis exploratorio</t>
-  </si>
-  <si>
     <t>Modelado</t>
   </si>
   <si>
-    <t>Selección de variables</t>
-  </si>
-  <si>
-    <t>Entrenamiento de modelos</t>
-  </si>
-  <si>
-    <t>Evaluación y comparación</t>
-  </si>
-  <si>
     <t>BI</t>
   </si>
   <si>
-    <t>Definición de KPIs</t>
-  </si>
-  <si>
-    <t>Construcción de dashboard</t>
-  </si>
-  <si>
     <t>Validación</t>
   </si>
   <si>
-    <t>Validación de resultados</t>
-  </si>
-  <si>
-    <t>Resultados</t>
-  </si>
-  <si>
-    <t>Interpretación y discusión</t>
-  </si>
-  <si>
     <t>Redacción</t>
   </si>
   <si>
-    <t>Capítulo IV Resultados</t>
-  </si>
-  <si>
-    <t>Capítulo V Conclusiones</t>
-  </si>
-  <si>
-    <t>Integración</t>
-  </si>
-  <si>
-    <t>Documento completo</t>
-  </si>
-  <si>
     <t>Correcciones</t>
   </si>
   <si>
@@ -267,12 +173,6 @@
   </si>
   <si>
     <t>Defensa</t>
-  </si>
-  <si>
-    <t>Presentación y ensayo</t>
-  </si>
-  <si>
-    <t>Entrega final</t>
   </si>
   <si>
     <t>Terminado</t>
@@ -425,41 +325,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -511,16 +377,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10128EF7-60C2-43B4-A723-CD25FC0BA309}" name="Tabla13" displayName="Tabla13" ref="A1:AD20" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10128EF7-60C2-43B4-A723-CD25FC0BA309}" name="Tabla13" displayName="Tabla13" ref="A1:AD20" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:AD20" xr:uid="{FEA64A45-B8C0-40A5-9558-FE32A9E3005A}"/>
   <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{3B51200C-56FE-492D-BA6F-F51AA338B09C}" name="ID"/>
     <tableColumn id="2" xr3:uid="{4E22F30B-C7CA-48A9-AFAD-148B9046592C}" name="Fase"/>
     <tableColumn id="3" xr3:uid="{56EB9B94-E2AF-41D2-882D-3F80F11E0087}" name="Actividad"/>
-    <tableColumn id="4" xr3:uid="{E6E2B9AA-D50E-42B9-9197-B7A874ED4BA7}" name="Inicio" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{6CA8853A-5DD7-4981-997C-3BC1D39AF7D9}" name="Fin" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{84883A31-CAF1-426B-BCB8-2CD472AF146D}" name="Duración (Sem)" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{81303626-6F82-4596-9BE9-CDB8C20C86E9}" name="% Avance" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{E6E2B9AA-D50E-42B9-9197-B7A874ED4BA7}" name="Inicio" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{6CA8853A-5DD7-4981-997C-3BC1D39AF7D9}" name="Fin" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{84883A31-CAF1-426B-BCB8-2CD472AF146D}" name="Duración (Sem)" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{81303626-6F82-4596-9BE9-CDB8C20C86E9}" name="% Avance" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{26543F28-D990-4D34-BC95-644789FD68EA}" name="Estado"/>
     <tableColumn id="9" xr3:uid="{5011571C-A403-4D1D-BA94-59F4EE1A874F}" name="S1"/>
     <tableColumn id="10" xr3:uid="{C1D0AF39-14AD-4710-B475-5364C710609B}" name="S2"/>
@@ -544,63 +410,6 @@
     <tableColumn id="28" xr3:uid="{7C52047F-E5C2-482A-828B-AA2E732E5488}" name="S20"/>
     <tableColumn id="29" xr3:uid="{C5CE32DB-BC07-43E3-AD13-D4D12DFB556C}" name="S21"/>
     <tableColumn id="30" xr3:uid="{ADF09E8E-AD0B-40D8-A5B5-1636E2BCD3D2}" name="S22"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FEA64A45-B8C0-40A5-9558-FE32A9E3005A}" name="Tabla1" displayName="Tabla1" ref="A1:AV23" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:AV23" xr:uid="{FEA64A45-B8C0-40A5-9558-FE32A9E3005A}"/>
-  <tableColumns count="48">
-    <tableColumn id="1" xr3:uid="{E1E711E6-765A-4697-ADC5-32B1A4385A80}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{377D250D-CC8F-4881-9856-3F5602268511}" name="Fase"/>
-    <tableColumn id="3" xr3:uid="{61D2D00F-BBB5-476E-A5E0-51D82D1E9A10}" name="Actividad"/>
-    <tableColumn id="4" xr3:uid="{BFC0FB89-2199-4A87-8E78-285D1CAE25B0}" name="Inicio" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{92C00F80-EF10-483D-94E4-AA2E43455A2E}" name="Fin" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{708CA2DB-1B87-4053-8243-7BF4090B61D6}" name="Duración (Sem)" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{F1C65CD7-1F88-46B6-84C2-579F3B36790C}" name="% Avance"/>
-    <tableColumn id="8" xr3:uid="{DD0C2500-C9A2-4B7E-942C-BC84BD21A7E3}" name="Estado"/>
-    <tableColumn id="9" xr3:uid="{60C5DA52-A107-42BA-8105-517EAD6CD4B1}" name="S1"/>
-    <tableColumn id="10" xr3:uid="{619638D0-04CD-4618-AF24-081DF1EE446D}" name="S2"/>
-    <tableColumn id="11" xr3:uid="{275D72B8-7424-4FB8-9A0C-FE8F9349C59C}" name="S3"/>
-    <tableColumn id="12" xr3:uid="{79FC4CF2-95C3-400B-8A78-1FB411879983}" name="S4"/>
-    <tableColumn id="13" xr3:uid="{83E01112-33AC-4B92-BE48-D3AB4739B58D}" name="S5"/>
-    <tableColumn id="14" xr3:uid="{0A2BD263-5BD1-47CB-9348-D91144576385}" name="S6"/>
-    <tableColumn id="15" xr3:uid="{EC199262-520C-45CF-B2BB-375FABA2D793}" name="S7"/>
-    <tableColumn id="16" xr3:uid="{F3E294B9-C60A-4690-9EDA-3AC13A1B08B7}" name="S8"/>
-    <tableColumn id="17" xr3:uid="{7F61E4BC-4C41-4BA2-9A6D-717705930FC4}" name="S9"/>
-    <tableColumn id="18" xr3:uid="{CD12E658-361C-4749-95DB-B41D5855E210}" name="S10"/>
-    <tableColumn id="19" xr3:uid="{65907E45-1D9D-428C-8E34-8673B22F495C}" name="S11"/>
-    <tableColumn id="20" xr3:uid="{E0B937CE-A063-45BE-A3BC-4FFFE910AA62}" name="S12"/>
-    <tableColumn id="21" xr3:uid="{0A473E41-BAFD-4D62-B885-F13A9CEA82E8}" name="S13"/>
-    <tableColumn id="22" xr3:uid="{5FF6C155-B76C-4643-9F84-70A4B3F9824C}" name="S14"/>
-    <tableColumn id="23" xr3:uid="{2EF249CC-647F-46F7-AF01-2E207AC532C9}" name="S15"/>
-    <tableColumn id="24" xr3:uid="{E4CD75A3-9B02-468F-9C97-BDE128E29056}" name="S16"/>
-    <tableColumn id="25" xr3:uid="{58B8B583-F911-4BE6-AFB2-8656300906E6}" name="S17"/>
-    <tableColumn id="26" xr3:uid="{7778A757-B679-4532-AC3B-780626467157}" name="S18"/>
-    <tableColumn id="27" xr3:uid="{42C5AFEE-33C2-4223-9AB4-52C9967521A1}" name="S19"/>
-    <tableColumn id="28" xr3:uid="{7617DDBD-EE76-482A-9496-707D8BCA0D32}" name="S20"/>
-    <tableColumn id="29" xr3:uid="{83640493-889E-48BA-8EAA-2AC58A1D5ACF}" name="S21"/>
-    <tableColumn id="30" xr3:uid="{2B428FD3-FF6B-4D2C-91A3-E1CAC03F8197}" name="S22"/>
-    <tableColumn id="31" xr3:uid="{39CB8BA2-D128-4F56-97EC-2C0A63561B27}" name="S23"/>
-    <tableColumn id="32" xr3:uid="{508426C7-662F-43E8-B37C-881268F8B93F}" name="S24"/>
-    <tableColumn id="33" xr3:uid="{0ADAD5B6-7D4F-46D1-BAF5-EC94669B974A}" name="S25"/>
-    <tableColumn id="34" xr3:uid="{9C1B86D1-E923-4FA3-A6BE-2FC9A7EBF356}" name="S26"/>
-    <tableColumn id="35" xr3:uid="{2C1C6B0F-1370-4F04-B525-8F079A00A2CE}" name="S27"/>
-    <tableColumn id="36" xr3:uid="{54D48F82-5672-40B8-AFB8-7BEAEF14E1D4}" name="S28"/>
-    <tableColumn id="37" xr3:uid="{9CEE7E4E-B31B-4E40-AB5E-DBAC4DDE49B2}" name="S29"/>
-    <tableColumn id="38" xr3:uid="{F598D934-DC1D-43B4-9937-00C0B07F80B1}" name="S30"/>
-    <tableColumn id="39" xr3:uid="{862DE33A-B944-4144-A9CD-91BAD477E09E}" name="S31"/>
-    <tableColumn id="40" xr3:uid="{E412465D-7242-4DB5-9BB7-AB22B00F96A2}" name="S32"/>
-    <tableColumn id="41" xr3:uid="{8ED37857-A668-434F-9E72-F32CB3F0C3E7}" name="S33"/>
-    <tableColumn id="42" xr3:uid="{32D69F86-58E1-4112-90EF-4709792D9A30}" name="S34"/>
-    <tableColumn id="43" xr3:uid="{8FDC0694-2A14-40C9-A0D4-4592D5F038CD}" name="S35"/>
-    <tableColumn id="44" xr3:uid="{F6021539-84DA-4068-8709-0686E5FDDC24}" name="S36"/>
-    <tableColumn id="45" xr3:uid="{9AD23370-E29D-47F2-9AAC-34849DD9F906}" name="S37"/>
-    <tableColumn id="46" xr3:uid="{B18E996E-DB4B-4DD3-A7E9-A1C5C546B461}" name="S38"/>
-    <tableColumn id="47" xr3:uid="{75C651F1-9E94-4570-8D34-112CAED14DB1}" name="S39"/>
-    <tableColumn id="48" xr3:uid="{25BF4A34-63C4-4217-935F-8571FDF83C30}" name="S40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1005,10 +814,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D2" s="9">
         <v>46132</v>
@@ -1023,7 +832,7 @@
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -1033,10 +842,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D3" s="9">
         <v>46146</v>
@@ -1051,7 +860,7 @@
         <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="K3" s="6"/>
     </row>
@@ -1060,10 +869,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D4" s="9">
         <v>46153</v>
@@ -1078,7 +887,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="L4" s="6"/>
     </row>
@@ -1087,10 +896,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D5" s="9">
         <v>46160</v>
@@ -1105,7 +914,7 @@
         <v>100</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="M5" s="6"/>
     </row>
@@ -1114,10 +923,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D6" s="9">
         <v>46167</v>
@@ -1132,7 +941,7 @@
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="N6" s="6"/>
     </row>
@@ -1141,10 +950,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D7" s="9">
         <v>46171</v>
@@ -1159,7 +968,7 @@
         <v>100</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="O7" s="6"/>
     </row>
@@ -1168,10 +977,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D8" s="9">
         <v>46174</v>
@@ -1186,7 +995,7 @@
         <v>100</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
@@ -1196,10 +1005,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D9" s="9">
         <v>46189</v>
@@ -1214,7 +1023,7 @@
         <v>100</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="P9" s="6"/>
     </row>
@@ -1223,10 +1032,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="D10" s="9">
         <v>46195</v>
@@ -1241,7 +1050,7 @@
         <v>100</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="6"/>
     </row>
@@ -1250,10 +1059,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="D11" s="9">
         <v>46202</v>
@@ -1268,7 +1077,7 @@
         <v>100</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="R11" s="6"/>
     </row>
@@ -1277,10 +1086,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D12" s="9">
         <v>46209</v>
@@ -1295,7 +1104,7 @@
         <v>100</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="S12" s="6"/>
     </row>
@@ -1304,10 +1113,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="D13" s="9">
         <v>46216</v>
@@ -1322,7 +1131,7 @@
         <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="T13" s="6"/>
       <c r="U13" s="6"/>
@@ -1332,10 +1141,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="D14" s="9">
         <v>46230</v>
@@ -1350,7 +1159,7 @@
         <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="V14" s="6"/>
     </row>
@@ -1359,10 +1168,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="D15" s="9">
         <v>46237</v>
@@ -1374,23 +1183,23 @@
         <v>2</v>
       </c>
       <c r="G15" s="10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
-      </c>
-      <c r="W15" s="11"/>
-      <c r="X15" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="W15" s="6"/>
+      <c r="X15" s="11"/>
     </row>
     <row r="16" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>14</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="D16" s="9">
         <v>46251</v>
@@ -1405,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Y16" s="5"/>
     </row>
@@ -1414,10 +1223,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="D17" s="9">
         <v>46258</v>
@@ -1432,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Z17" s="5"/>
       <c r="AA17" s="5"/>
@@ -1442,10 +1251,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D18" s="9">
         <v>46272</v>
@@ -1460,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AB18" s="5"/>
     </row>
@@ -1469,10 +1278,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D19" s="9">
         <v>46279</v>
@@ -1487,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AC19" s="5"/>
     </row>
@@ -1496,10 +1305,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="D20" s="9">
         <v>46286</v>
@@ -1514,795 +1323,9 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AD20" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFF0000"/>
-  </sheetPr>
-  <dimension ref="A1:AV23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="4.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="4.88671875" customWidth="1"/>
-    <col min="18" max="48" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3">
-        <v>46147</v>
-      </c>
-      <c r="E2" s="3">
-        <v>46160</v>
-      </c>
-      <c r="F2" s="4">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>100</v>
-      </c>
-      <c r="H2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="3">
-        <v>46161</v>
-      </c>
-      <c r="E3" s="3">
-        <v>46167</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-      <c r="H3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="3">
-        <v>46168</v>
-      </c>
-      <c r="E4" s="3">
-        <v>46188</v>
-      </c>
-      <c r="F4" s="4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="3">
-        <v>46189</v>
-      </c>
-      <c r="E5" s="3">
-        <v>46209</v>
-      </c>
-      <c r="F5" s="4">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
-      <c r="H5" t="s">
-        <v>84</v>
-      </c>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-    </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="3">
-        <v>46210</v>
-      </c>
-      <c r="E6" s="3">
-        <v>46223</v>
-      </c>
-      <c r="F6" s="4">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>100</v>
-      </c>
-      <c r="H6" t="s">
-        <v>84</v>
-      </c>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-    </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="3">
-        <v>46224</v>
-      </c>
-      <c r="E7" s="3">
-        <v>46237</v>
-      </c>
-      <c r="F7" s="4">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>100</v>
-      </c>
-      <c r="H7" t="s">
-        <v>84</v>
-      </c>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="3">
-        <v>46238</v>
-      </c>
-      <c r="E8" s="3">
-        <v>46251</v>
-      </c>
-      <c r="F8" s="4">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>100</v>
-      </c>
-      <c r="H8" t="s">
-        <v>84</v>
-      </c>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-    </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="3">
-        <v>46252</v>
-      </c>
-      <c r="E9" s="3">
-        <v>46265</v>
-      </c>
-      <c r="F9" s="4">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9" t="s">
-        <v>84</v>
-      </c>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-    </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="3">
-        <v>46266</v>
-      </c>
-      <c r="E10" s="3">
-        <v>46279</v>
-      </c>
-      <c r="F10" s="4">
-        <v>2</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-    </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="3">
-        <v>46280</v>
-      </c>
-      <c r="E11" s="3">
-        <v>46286</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB11" s="5"/>
-    </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="3">
-        <v>46287</v>
-      </c>
-      <c r="E12" s="3">
-        <v>46307</v>
-      </c>
-      <c r="F12" s="4">
-        <v>3</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5"/>
-      <c r="AE12" s="5"/>
-    </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="3">
-        <v>46308</v>
-      </c>
-      <c r="E13" s="3">
-        <v>46321</v>
-      </c>
-      <c r="F13" s="4">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="5"/>
-    </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="3">
-        <v>46322</v>
-      </c>
-      <c r="E14" s="3">
-        <v>46328</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH14" s="5"/>
-    </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="3">
-        <v>46329</v>
-      </c>
-      <c r="E15" s="3">
-        <v>46342</v>
-      </c>
-      <c r="F15" s="4">
-        <v>2</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI15" s="5"/>
-      <c r="AJ15" s="5"/>
-    </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" s="3">
-        <v>46343</v>
-      </c>
-      <c r="E16" s="3">
-        <v>46356</v>
-      </c>
-      <c r="F16" s="4">
-        <v>2</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK16" s="5"/>
-      <c r="AL16" s="5"/>
-    </row>
-    <row r="17" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="3">
-        <v>46357</v>
-      </c>
-      <c r="E17" s="3">
-        <v>46370</v>
-      </c>
-      <c r="F17" s="4">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM17" s="5"/>
-      <c r="AN17" s="5"/>
-    </row>
-    <row r="18" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="3">
-        <v>46371</v>
-      </c>
-      <c r="E18" s="3">
-        <v>46384</v>
-      </c>
-      <c r="F18" s="4">
-        <v>2</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" t="s">
-        <v>50</v>
-      </c>
-      <c r="AO18" s="5"/>
-      <c r="AP18" s="5"/>
-    </row>
-    <row r="19" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="3">
-        <v>46385</v>
-      </c>
-      <c r="E19" s="3">
-        <v>46391</v>
-      </c>
-      <c r="F19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19" t="s">
-        <v>50</v>
-      </c>
-      <c r="AQ19" s="5"/>
-    </row>
-    <row r="20" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="3">
-        <v>46392</v>
-      </c>
-      <c r="E20" s="3">
-        <v>46405</v>
-      </c>
-      <c r="F20" s="4">
-        <v>2</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR20" s="5"/>
-      <c r="AS20" s="5"/>
-    </row>
-    <row r="21" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="3">
-        <v>46406</v>
-      </c>
-      <c r="E21" s="3">
-        <v>46419</v>
-      </c>
-      <c r="F21" s="4">
-        <v>2</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AT21" s="5"/>
-      <c r="AU21" s="5"/>
-    </row>
-    <row r="22" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="3">
-        <v>46420</v>
-      </c>
-      <c r="E22" s="3">
-        <v>46426</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV22" s="5"/>
-    </row>
-    <row r="23" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="3">
-        <v>46427</v>
-      </c>
-      <c r="E23" s="3">
-        <v>46433</v>
-      </c>
-      <c r="F23" s="4">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV23" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/documentacion/Plan_Tesis_2026_Gantt_Seguimiento.xlsx
+++ b/documentacion/Plan_Tesis_2026_Gantt_Seguimiento.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\tesis\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F47E95C-8714-41C0-B8AC-26A50C4F7FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A3939C-9065-4939-8C23-C4DCC07B30CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="68">
   <si>
     <t>ID</t>
   </si>
@@ -209,6 +209,21 @@
   </si>
   <si>
     <t>Entrenar modelos</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>JUNIO</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
   </si>
 </sst>
 </file>
@@ -236,7 +251,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,7 +277,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -321,6 +342,10 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,8 +402,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10128EF7-60C2-43B4-A723-CD25FC0BA309}" name="Tabla13" displayName="Tabla13" ref="A1:AD20" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:AD20" xr:uid="{FEA64A45-B8C0-40A5-9558-FE32A9E3005A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10128EF7-60C2-43B4-A723-CD25FC0BA309}" name="Tabla13" displayName="Tabla13" ref="A2:AD39" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A2:AD39" xr:uid="{FEA64A45-B8C0-40A5-9558-FE32A9E3005A}"/>
   <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{3B51200C-56FE-492D-BA6F-F51AA338B09C}" name="ID"/>
     <tableColumn id="2" xr3:uid="{4E22F30B-C7CA-48A9-AFAD-148B9046592C}" name="Fase"/>
@@ -703,12 +728,12 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AD39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="38.77734375" customWidth="1"/>
     <col min="4" max="5" width="11.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.109375" style="4" customWidth="1"/>
     <col min="7" max="7" width="11" style="4" customWidth="1"/>
@@ -717,144 +742,148 @@
     <col min="18" max="30" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="I1" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+    </row>
+    <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="9">
-        <v>46132</v>
-      </c>
-      <c r="E2" s="9">
-        <v>46145</v>
-      </c>
-      <c r="F2" s="10">
-        <v>2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>100</v>
-      </c>
-      <c r="H2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
     </row>
     <row r="3" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="E3" s="9">
-        <v>46152</v>
+        <v>46145</v>
       </c>
       <c r="F3" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="10">
         <v>100</v>
@@ -862,50 +891,35 @@
       <c r="H3" t="s">
         <v>51</v>
       </c>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="9">
-        <v>46153</v>
-      </c>
-      <c r="E4" s="9">
-        <v>46159</v>
-      </c>
-      <c r="F4" s="10">
-        <v>1</v>
-      </c>
-      <c r="G4" s="10">
-        <v>100</v>
-      </c>
-      <c r="H4" t="s">
-        <v>51</v>
-      </c>
-      <c r="L4" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D5" s="9">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="E5" s="9">
-        <v>46166</v>
+        <v>46152</v>
       </c>
       <c r="F5" s="10">
         <v>1</v>
@@ -916,159 +930,107 @@
       <c r="H5" t="s">
         <v>51</v>
       </c>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7">
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="K6" s="11"/>
+    </row>
+    <row r="7" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="9">
+        <v>46153</v>
+      </c>
+      <c r="E7" s="9">
+        <v>46159</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10">
+        <v>100</v>
+      </c>
+      <c r="H7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>4</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="9">
+        <v>46160</v>
+      </c>
+      <c r="E9" s="9">
+        <v>46166</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10">
+        <v>100</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="M10" s="11"/>
+    </row>
+    <row r="11" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D11" s="9">
         <v>46167</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E11" s="9">
         <v>46170</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10">
-        <v>100</v>
-      </c>
-      <c r="H6" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="9">
-        <v>46171</v>
-      </c>
-      <c r="E7" s="9">
-        <v>46173</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="10">
-        <v>100</v>
-      </c>
-      <c r="H7" t="s">
-        <v>51</v>
-      </c>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="9">
-        <v>46174</v>
-      </c>
-      <c r="E8" s="9">
-        <v>46188</v>
-      </c>
-      <c r="F8" s="10">
-        <v>2</v>
-      </c>
-      <c r="G8" s="10">
-        <v>100</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="9">
-        <v>46189</v>
-      </c>
-      <c r="E9" s="9">
-        <v>46192</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="10">
-        <v>100</v>
-      </c>
-      <c r="H9" t="s">
-        <v>51</v>
-      </c>
-      <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="9">
-        <v>46195</v>
-      </c>
-      <c r="E10" s="9">
-        <v>46201</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="10">
-        <v>100</v>
-      </c>
-      <c r="H10" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q10" s="6"/>
-    </row>
-    <row r="11" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="9">
-        <v>46202</v>
-      </c>
-      <c r="E11" s="9">
-        <v>46208</v>
       </c>
       <c r="F11" s="10">
         <v>1</v>
@@ -1079,255 +1041,547 @@
       <c r="H11" t="s">
         <v>51</v>
       </c>
-      <c r="R11" s="6"/>
-    </row>
-    <row r="12" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="9">
-        <v>46209</v>
-      </c>
-      <c r="E12" s="9">
-        <v>46213</v>
-      </c>
-      <c r="F12" s="10">
-        <v>1</v>
-      </c>
-      <c r="G12" s="10">
-        <v>100</v>
-      </c>
-      <c r="H12" t="s">
-        <v>52</v>
-      </c>
-      <c r="S12" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="N12" s="11"/>
     </row>
     <row r="13" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D13" s="9">
-        <v>46216</v>
+        <v>46171</v>
       </c>
       <c r="E13" s="9">
-        <v>46229</v>
+        <v>46173</v>
       </c>
       <c r="F13" s="10">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="G13" s="10">
         <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
-      </c>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-    </row>
-    <row r="14" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
-        <v>12</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="9">
-        <v>46230</v>
-      </c>
-      <c r="E14" s="9">
-        <v>46236</v>
-      </c>
-      <c r="F14" s="10">
-        <v>1</v>
-      </c>
-      <c r="G14" s="10">
-        <v>100</v>
-      </c>
-      <c r="H14" t="s">
-        <v>32</v>
-      </c>
-      <c r="V14" s="6"/>
+        <v>51</v>
+      </c>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="O14" s="11"/>
     </row>
     <row r="15" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D15" s="9">
-        <v>46237</v>
+        <v>46174</v>
       </c>
       <c r="E15" s="9">
-        <v>46250</v>
+        <v>46188</v>
       </c>
       <c r="F15" s="10">
         <v>2</v>
       </c>
       <c r="G15" s="10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
-      </c>
-      <c r="W15" s="6"/>
-      <c r="X15" s="11"/>
-    </row>
-    <row r="16" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
-        <v>14</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="9">
-        <v>46251</v>
-      </c>
-      <c r="E16" s="9">
-        <v>46257</v>
-      </c>
-      <c r="F16" s="10">
-        <v>1</v>
-      </c>
-      <c r="G16" s="10">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y16" s="5"/>
-    </row>
-    <row r="17" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+    </row>
+    <row r="17" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D17" s="9">
-        <v>46258</v>
+        <v>46189</v>
       </c>
       <c r="E17" s="9">
-        <v>46271</v>
+        <v>46192</v>
       </c>
       <c r="F17" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z17" s="5"/>
-      <c r="AA17" s="5"/>
-    </row>
-    <row r="18" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7">
-        <v>16</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="9">
-        <v>46272</v>
-      </c>
-      <c r="E18" s="9">
-        <v>46278</v>
-      </c>
-      <c r="F18" s="10">
-        <v>1</v>
-      </c>
-      <c r="G18" s="10">
-        <v>0</v>
-      </c>
-      <c r="H18" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB18" s="5"/>
-    </row>
-    <row r="19" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="1:27" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="P18" s="11"/>
+    </row>
+    <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D19" s="9">
-        <v>46279</v>
+        <v>46195</v>
       </c>
       <c r="E19" s="9">
-        <v>46285</v>
+        <v>46201</v>
       </c>
       <c r="F19" s="10">
         <v>1</v>
       </c>
       <c r="G19" s="10">
+        <v>100</v>
+      </c>
+      <c r="H19" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="1:27" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="Q20" s="11"/>
+    </row>
+    <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
+        <v>10</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="9">
+        <v>46202</v>
+      </c>
+      <c r="E21" s="9">
+        <v>46208</v>
+      </c>
+      <c r="F21" s="10">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10">
+        <v>100</v>
+      </c>
+      <c r="H21" t="s">
+        <v>51</v>
+      </c>
+      <c r="R21" s="6"/>
+    </row>
+    <row r="22" spans="1:27" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="R22" s="11"/>
+    </row>
+    <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="7">
+        <v>11</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="9">
+        <v>46209</v>
+      </c>
+      <c r="E23" s="9">
+        <v>46213</v>
+      </c>
+      <c r="F23" s="10">
+        <v>1</v>
+      </c>
+      <c r="G23" s="10">
+        <v>100</v>
+      </c>
+      <c r="H23" t="s">
+        <v>51</v>
+      </c>
+      <c r="S23" s="6"/>
+    </row>
+    <row r="24" spans="1:27" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+    </row>
+    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="7">
+        <v>11</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="9">
+        <v>46216</v>
+      </c>
+      <c r="E25" s="9">
+        <v>46229</v>
+      </c>
+      <c r="F25" s="10">
+        <v>3</v>
+      </c>
+      <c r="G25" s="10">
+        <v>100</v>
+      </c>
+      <c r="H25" t="s">
+        <v>51</v>
+      </c>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+    </row>
+    <row r="26" spans="1:27" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
+    </row>
+    <row r="27" spans="1:27" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="7">
+        <v>12</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="9">
+        <v>46230</v>
+      </c>
+      <c r="E27" s="9">
+        <v>46236</v>
+      </c>
+      <c r="F27" s="10">
+        <v>1</v>
+      </c>
+      <c r="G27" s="10">
+        <v>100</v>
+      </c>
+      <c r="H27" t="s">
+        <v>51</v>
+      </c>
+      <c r="V27" s="6"/>
+    </row>
+    <row r="28" spans="1:27" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="X28" s="11"/>
+      <c r="Y28" s="11"/>
+    </row>
+    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="7">
+        <v>13</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="9">
+        <v>46237</v>
+      </c>
+      <c r="E29" s="9">
+        <v>46250</v>
+      </c>
+      <c r="F29" s="10">
+        <v>2</v>
+      </c>
+      <c r="G29" s="10">
+        <v>100</v>
+      </c>
+      <c r="H29" t="s">
+        <v>51</v>
+      </c>
+      <c r="W29" s="6"/>
+      <c r="X29" s="6"/>
+    </row>
+    <row r="30" spans="1:27" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="Z30" s="11"/>
+    </row>
+    <row r="31" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="7">
+        <v>14</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="9">
+        <v>46251</v>
+      </c>
+      <c r="E31" s="9">
+        <v>46257</v>
+      </c>
+      <c r="F31" s="10">
+        <v>1</v>
+      </c>
+      <c r="G31" s="10">
+        <v>100</v>
+      </c>
+      <c r="H31" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y31" s="6"/>
+    </row>
+    <row r="32" spans="1:27" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="Z32" s="11"/>
+      <c r="AA32" s="11"/>
+    </row>
+    <row r="33" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="7">
+        <v>15</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="9">
+        <v>46258</v>
+      </c>
+      <c r="E33" s="9">
+        <v>46271</v>
+      </c>
+      <c r="F33" s="10">
+        <v>2</v>
+      </c>
+      <c r="G33" s="10">
+        <v>100</v>
+      </c>
+      <c r="H33" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6"/>
+    </row>
+    <row r="34" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="Z34" s="11"/>
+      <c r="AA34" s="11"/>
+      <c r="AB34" s="11"/>
+    </row>
+    <row r="35" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="7">
+        <v>16</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="9">
+        <v>46272</v>
+      </c>
+      <c r="E35" s="9">
+        <v>46278</v>
+      </c>
+      <c r="F35" s="10">
+        <v>1</v>
+      </c>
+      <c r="G35" s="10">
+        <v>100</v>
+      </c>
+      <c r="H35" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB35" s="12"/>
+    </row>
+    <row r="36" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="7"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="AB36" s="12"/>
+    </row>
+    <row r="37" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="7">
+        <v>17</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="9">
+        <v>46279</v>
+      </c>
+      <c r="E37" s="9">
+        <v>46285</v>
+      </c>
+      <c r="F37" s="10">
+        <v>1</v>
+      </c>
+      <c r="G37" s="10">
         <v>0</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H37" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC37" s="5"/>
+    </row>
+    <row r="38" spans="1:30" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="7"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="AC38" s="5"/>
+    </row>
+    <row r="39" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="7">
+        <v>18</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="9">
+        <v>46286</v>
+      </c>
+      <c r="E39" s="9">
+        <v>46292</v>
+      </c>
+      <c r="F39" s="10">
+        <v>1</v>
+      </c>
+      <c r="G39" s="10">
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
         <v>32</v>
       </c>
-      <c r="AC19" s="5"/>
-    </row>
-    <row r="20" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
-        <v>18</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="9">
-        <v>46286</v>
-      </c>
-      <c r="E20" s="9">
-        <v>46292</v>
-      </c>
-      <c r="F20" s="10">
-        <v>1</v>
-      </c>
-      <c r="G20" s="10">
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD20" s="5"/>
+      <c r="AD39" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="I1:K1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
